--- a/GUA/IPPU/A1_Outputs/A-O_AR_Model_Base_Year.xlsx
+++ b/GUA/IPPU/A1_Outputs/A-O_AR_Model_Base_Year.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\GUA_Modelos_Sectoriales_2024\M0_IPPU\A1_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\0_guatemala_2025\IPPU_GUA_v1_2025\A1_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C3D5E5-2493-45E1-829B-DD6E34491834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D41FFC-05F2-4DD0-88FB-1C30399CC03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Primary" sheetId="1" r:id="rId1"/>
     <sheet name="Secondary" sheetId="2" r:id="rId2"/>
     <sheet name="Demand Techs" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Demand Techs'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Primary!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Secondary!$A$1:$J$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="122">
   <si>
     <t>Tech</t>
   </si>
@@ -61,18 +66,36 @@
     <t>RAW_MAT_CEM</t>
   </si>
   <si>
+    <t>IMP_STOR</t>
+  </si>
+  <si>
+    <t>PARAFFIN</t>
+  </si>
+  <si>
     <t>Supply of raw material for clinker</t>
   </si>
   <si>
     <t>Supply of raw material for cement</t>
   </si>
   <si>
+    <t>Imports or storage of Clinker</t>
+  </si>
+  <si>
+    <t>Use of Paraffin Wax</t>
+  </si>
+  <si>
+    <t>CLK_PROD</t>
+  </si>
+  <si>
     <t>Raw materials for clinker</t>
   </si>
   <si>
     <t>Raw materials for cement</t>
   </si>
   <si>
+    <t>Clinker production</t>
+  </si>
+  <si>
     <t>Fuel.I</t>
   </si>
   <si>
@@ -97,37 +120,292 @@
     <t>Cement production</t>
   </si>
   <si>
-    <t>Mton</t>
-  </si>
-  <si>
-    <t>Mt clinker</t>
+    <t>CEM_PROD</t>
+  </si>
+  <si>
+    <t>T5CEM_PRODIND</t>
+  </si>
+  <si>
+    <t>T5PARAFFINIPPU</t>
+  </si>
+  <si>
+    <t>Demand Cement production for Industrial</t>
+  </si>
+  <si>
+    <t>Demand Use of Paraffin Wax for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5INDCEM_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPUPARAFFIN</t>
+  </si>
+  <si>
+    <t>Demand Industrial Cement production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Use of Paraffin Wax</t>
+  </si>
+  <si>
+    <t>LUBRI_OILS</t>
+  </si>
+  <si>
+    <t>Use of Lubricants Oils</t>
+  </si>
+  <si>
+    <t>T5LUBRI_OILSIPPU</t>
+  </si>
+  <si>
+    <t>Demand Use of Lubricants Oils for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPULUBRI_OILS</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Use of Lubricants Oils</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC32</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC125</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC134a</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC143a</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC32IPPU</t>
+  </si>
+  <si>
+    <t>Demand Refrigeration and air conditioning HFC32 for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC32</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC125IPPU</t>
+  </si>
+  <si>
+    <t>Demand Refrigeration and air conditioning HFC125 for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC125</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC134aIPPU</t>
+  </si>
+  <si>
+    <t>Demand Refrigeration and air conditioning HFC134a for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC134a</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC143aIPPU</t>
+  </si>
+  <si>
+    <t>Demand Refrigeration and air conditioning HFC143a for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC143a</t>
+  </si>
+  <si>
+    <t>PROD_FERRO</t>
+  </si>
+  <si>
+    <t>Ferroalloy production</t>
+  </si>
+  <si>
+    <t>T5PROD_FERROIPPU</t>
+  </si>
+  <si>
+    <t>Demand Ferroalloy production for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUPROD_FERRO</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Ferroalloy production</t>
+  </si>
+  <si>
+    <t>Mt lime</t>
+  </si>
+  <si>
+    <t>MtFeNi</t>
+  </si>
+  <si>
+    <t>Mt paraffin wax</t>
+  </si>
+  <si>
+    <t>Mt material</t>
+  </si>
+  <si>
+    <t>Mt Clinker</t>
   </si>
   <si>
     <t>Mt cemento</t>
   </si>
   <si>
-    <t>Mt materiales</t>
-  </si>
-  <si>
-    <t>CLK_PROD</t>
-  </si>
-  <si>
-    <t>Clinker production</t>
-  </si>
-  <si>
-    <t>CEM_PROD</t>
-  </si>
-  <si>
-    <t>T5CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
-    <t>Demand Cement production for Cement production</t>
-  </si>
-  <si>
-    <t>E5_CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
-    <t>Demand Cement production Cement production</t>
+    <t>GLASS_PROD</t>
+  </si>
+  <si>
+    <t>Glass production</t>
+  </si>
+  <si>
+    <t>Mt glass</t>
+  </si>
+  <si>
+    <t>IRON_STEEL</t>
+  </si>
+  <si>
+    <t>Iron and Steel production</t>
+  </si>
+  <si>
+    <t>T5GLASS_PRODIPPU</t>
+  </si>
+  <si>
+    <t>Demand Glass production for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUGLASS_PROD</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Glass production</t>
+  </si>
+  <si>
+    <t>T5IRON_STEELIPPU</t>
+  </si>
+  <si>
+    <t>Demand Iron and Steel production for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUIRON_STEEL</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Iron and Steel production</t>
+  </si>
+  <si>
+    <t>Mt steel</t>
+  </si>
+  <si>
+    <t>LIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>Lime production calcitic</t>
+  </si>
+  <si>
+    <t>LIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>Lime production dolomitic</t>
+  </si>
+  <si>
+    <t>CARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>Carbonate ceramics</t>
+  </si>
+  <si>
+    <t>CARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>Carbonate soda ash</t>
+  </si>
+  <si>
+    <t>T5LIME_CAL_PRODIPPU</t>
+  </si>
+  <si>
+    <t>T5LIME_DOL_PRODIPPU</t>
+  </si>
+  <si>
+    <t>Demand Lime production calcitic for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Lime production calcitic</t>
+  </si>
+  <si>
+    <t>Demand Lime production dolomitic for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Lime production dolomitic</t>
+  </si>
+  <si>
+    <t>T5CARBONATE_CERAMICSIPPU</t>
+  </si>
+  <si>
+    <t>Demand Carbonate ceramics for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Carbonate ceramics</t>
+  </si>
+  <si>
+    <t>T5CARBONATE_ASHIPPU</t>
+  </si>
+  <si>
+    <t>Demand Carbonate soda ash for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Carbonate soda ash</t>
+  </si>
+  <si>
+    <t>Mt libricantes</t>
+  </si>
+  <si>
+    <t>Mt lubricantes</t>
+  </si>
+  <si>
+    <t>Mt carbonatos</t>
+  </si>
+  <si>
+    <t>ktHFC143a</t>
+  </si>
+  <si>
+    <t>ktHFC134a</t>
+  </si>
+  <si>
+    <t>ktHFC125</t>
+  </si>
+  <si>
+    <t>ktHFC32</t>
   </si>
 </sst>
 </file>
@@ -135,9 +413,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,15 +431,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,13 +441,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -205,21 +470,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Millares [0] 2" xfId="1" xr:uid="{75B7E820-626F-4B01-BB72-39E4E05344E1}"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -522,15 +785,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -554,46 +817,327 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -601,32 +1145,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -648,134 +1192,136 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.69099999999999995</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="3">
         <v>0.30900000000000005</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="67.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="64.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -797,35 +1343,427 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+      <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1073,7 +2011,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8EAB3EB-028F-470D-9A5D-8856B5543092}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{592ACB52-672D-4764-A9CE-09110CB7A555}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -1081,9 +2019,32 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E6A6AE8-DA9B-423D-8C3E-E82D924777FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F6A45C5-8406-40FB-895A-33E7F662202E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A3277F-9686-429F-8591-D5AF61114654}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F3E225-3E53-4EA6-B1C8-2BAD8DD8CF07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>